--- a/docs/downloads/sharepoint-administrator-checklist.xlsx
+++ b/docs/downloads/sharepoint-administrator-checklist.xlsx
@@ -526,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -546,7 +546,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: SharePoint Admin  |  FSI Agent Governance Framework v1.2.41 — February 2026</t>
+          <t>Role: SharePoint Admin  |  FSI Agent Governance Framework v1.3.0 — March 2026</t>
         </is>
       </c>
     </row>
@@ -711,10 +711,48 @@
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="7" t="n"/>
     </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>FSI Agent Governance Framework v1.2.41 — February 2026</t>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Item-Level Permission Scanning for Agent Knowledge Sources</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="11" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Embedded File Content Governance</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>FSI Agent Governance Framework v1.3.0 — March 2026</t>
         </is>
       </c>
     </row>
@@ -722,11 +760,11 @@
   <autoFilter ref="A4:E4"/>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A15:E15"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C5:C11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Status" error="Please select: Not Started, In Progress, Completed, or N/A" promptTitle="Status" prompt="Select implementation status" type="list">
+    <dataValidation sqref="C5:C13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Status" error="Please select: Not Started, In Progress, Completed, or N/A" promptTitle="Status" prompt="Select implementation status" type="list">
       <formula1>"Not Started,In Progress,Completed,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -734,7 +772,7 @@
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;CSharePoint Administrator Checklist</oddHeader>
-    <oddFooter>&amp;CFSI Agent Governance Framework v1.2.41 — February 2026</oddFooter>
+    <oddFooter>&amp;CFSI Agent Governance Framework v1.3.0 — March 2026</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/docs/downloads/sharepoint-administrator-checklist.xlsx
+++ b/docs/downloads/sharepoint-administrator-checklist.xlsx
@@ -546,7 +546,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: SharePoint Admin  |  FSI Agent Governance Framework v1.3.0 — March 2026</t>
+          <t>Role: SharePoint Admin  |  FSI Agent Governance Framework v1.4.0 — April 2026</t>
         </is>
       </c>
     </row>
@@ -749,10 +749,11 @@
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="7" t="n"/>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>FSI Agent Governance Framework v1.3.0 — March 2026</t>
+          <t>FSI Agent Governance Framework v1.4.0 — April 2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/sharepoint-administrator-checklist.xlsx
+++ b/docs/downloads/sharepoint-administrator-checklist.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SharePoint Admin" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SharePoint Admin" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SharePoint Admin'!$A$4:$E$4</definedName>
@@ -546,7 +546,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: SharePoint Admin  |  FSI Agent Governance Framework v1.4.0 — April 2026</t>
+          <t>Role: SharePoint Admin  |  FSI Agent Governance Framework v1.6.2 — May 2026</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>SharePoint Information Access Governance (IAG)</t>
+          <t>SharePoint Information Access Governance (IAG) / Restricted Content Discovery</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>FSI Agent Governance Framework v1.4.0 — April 2026</t>
+          <t>FSI Agent Governance Framework v1.6.2 — May 2026</t>
         </is>
       </c>
     </row>
